--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008407015632763826</v>
       </c>
       <c r="C2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9817839</v>
+        <v>4830404</v>
       </c>
       <c r="L2" t="n">
-        <v>6067341</v>
+        <v>2912632</v>
       </c>
       <c r="M2" t="n">
-        <v>1486138</v>
+        <v>708478</v>
       </c>
       <c r="N2" t="n">
-        <v>67897</v>
+        <v>29250</v>
       </c>
       <c r="O2" t="n">
-        <v>883331</v>
+        <v>419194</v>
       </c>
       <c r="P2" t="n">
-        <v>331177</v>
+        <v>160798</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998530149459839</v>
+        <v>0.999843418598175</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9595112204551697</v>
+        <v>0.9390422105789185</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9040683507919312</v>
+        <v>0.8744302988052368</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8942252397537231</v>
+        <v>0.844319760799408</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3417869210243225</v>
+        <v>0.3059431314468384</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8988258838653564</v>
+        <v>0.8651398420333862</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9441859722137451</v>
+        <v>0.9214257001876831</v>
       </c>
       <c r="X2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567423462867737</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911146342754364</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582749962806702</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627725958824158</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020447134971619</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,130 +792,130 @@
         <v>0.002014765064493864</v>
       </c>
       <c r="C3" t="n">
-        <v>1383</v>
+        <v>691</v>
       </c>
       <c r="D3" t="n">
-        <v>9817839</v>
+        <v>4830404</v>
       </c>
       <c r="E3" t="n">
-        <v>320323</v>
+        <v>235770</v>
       </c>
       <c r="F3" t="n">
-        <v>3222</v>
+        <v>1982</v>
       </c>
       <c r="G3" t="n">
-        <v>512</v>
+        <v>363</v>
       </c>
       <c r="H3" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>20137374</v>
+        <v>10068626</v>
       </c>
       <c r="K3" t="n">
-        <v>22274298</v>
+        <v>11033128</v>
       </c>
       <c r="L3" t="n">
-        <v>25642390</v>
+        <v>12722878</v>
       </c>
       <c r="M3" t="n">
-        <v>30789345</v>
+        <v>15351657</v>
       </c>
       <c r="N3" t="n">
-        <v>32522790</v>
+        <v>16260379</v>
       </c>
       <c r="O3" t="n">
-        <v>31714408</v>
+        <v>15841462</v>
       </c>
       <c r="P3" t="n">
-        <v>32425878</v>
+        <v>16209006</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9679026007652283</v>
+        <v>0.952872633934021</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9269062280654907</v>
+        <v>0.8893904685974121</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7960608005523682</v>
+        <v>0.758777379989624</v>
       </c>
       <c r="U3" t="n">
-        <v>0.380473405122757</v>
+        <v>0.3276760280132294</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8675740957260132</v>
+        <v>0.8232516646385193</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8567618131637573</v>
+        <v>0.8319346904754639</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>398208</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17110</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13592</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20139240</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22249364</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25705317</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30700729</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32593417</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31714153</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32418947</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577006697654724</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099981188774109</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85770583152771</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6622154712677002</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015981554985046</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03183674520492466</v>
       </c>
       <c r="C4" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>382415</v>
+        <v>290110</v>
       </c>
       <c r="E4" t="n">
-        <v>6067341</v>
+        <v>2912632</v>
       </c>
       <c r="F4" t="n">
-        <v>93612</v>
+        <v>70002</v>
       </c>
       <c r="G4" t="n">
-        <v>1486</v>
+        <v>1235</v>
       </c>
       <c r="H4" t="n">
-        <v>822</v>
+        <v>806</v>
       </c>
       <c r="I4" t="n">
         <v>33</v>
       </c>
       <c r="J4" t="n">
-        <v>1866</v>
+        <v>994</v>
       </c>
       <c r="K4" t="n">
-        <v>414286</v>
+        <v>313565</v>
       </c>
       <c r="L4" t="n">
-        <v>643812</v>
+        <v>418259</v>
       </c>
       <c r="M4" t="n">
-        <v>175790</v>
+        <v>130633</v>
       </c>
       <c r="N4" t="n">
-        <v>130756</v>
+        <v>66356</v>
       </c>
       <c r="O4" t="n">
-        <v>99430</v>
+        <v>65345</v>
       </c>
       <c r="P4" t="n">
-        <v>19577</v>
+        <v>13712</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999265074729919</v>
+        <v>0.9999217391014099</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9636886119842529</v>
+        <v>0.9459068775177002</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9153448343276978</v>
+        <v>0.8818469047546387</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8422925472259521</v>
+        <v>0.7992662787437439</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3600940704345703</v>
+        <v>0.3164368569850922</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8829234838485718</v>
+        <v>0.8436761498451233</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8983519673347473</v>
+        <v>0.8743963837623596</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>410116</v>
+        <v>204986</v>
       </c>
       <c r="Z4" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AA4" t="n">
-        <v>165604</v>
+        <v>82895</v>
       </c>
       <c r="AB4" t="n">
-        <v>10994</v>
+        <v>5498</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>439220</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>580885</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>264406</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60129</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99685</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572212696075439</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9105718731880188</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579903244972229</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.662493884563446</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018213748931885</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>21309</v>
+        <v>14847</v>
       </c>
       <c r="E5" t="n">
-        <v>280416</v>
+        <v>163042</v>
       </c>
       <c r="F5" t="n">
-        <v>1486138</v>
+        <v>708478</v>
       </c>
       <c r="G5" t="n">
-        <v>53719</v>
+        <v>23660</v>
       </c>
       <c r="H5" t="n">
-        <v>24712</v>
+        <v>23131</v>
       </c>
       <c r="I5" t="n">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>325577</v>
+        <v>238903</v>
       </c>
       <c r="L5" t="n">
-        <v>478457</v>
+        <v>362231</v>
       </c>
       <c r="M5" t="n">
-        <v>380727</v>
+        <v>225232</v>
       </c>
       <c r="N5" t="n">
-        <v>110557</v>
+        <v>60015</v>
       </c>
       <c r="O5" t="n">
-        <v>134831</v>
+        <v>89999</v>
       </c>
       <c r="P5" t="n">
-        <v>55368</v>
+        <v>32484</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999431371688843</v>
+        <v>0.9999394416809082</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9774652123451233</v>
+        <v>0.9663457870483398</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9658178091049194</v>
+        <v>0.9524555206298828</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9830495715141296</v>
+        <v>0.9783220887184143</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9926500916481018</v>
+        <v>0.9923019409179688</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9928648471832275</v>
+        <v>0.9905370473861694</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9977173209190369</v>
+        <v>0.9971859455108643</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16069</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>170194</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19877</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58238</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>429060</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>589134</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>265644</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60279</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100189</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735538363456726</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643634557723999</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983855664730072</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996332585811615</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939122200012207</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983846545219421</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D6" t="n">
-        <v>10524</v>
+        <v>8576</v>
       </c>
       <c r="E6" t="n">
-        <v>42011</v>
+        <v>18413</v>
       </c>
       <c r="F6" t="n">
-        <v>37370</v>
+        <v>22574</v>
       </c>
       <c r="G6" t="n">
-        <v>67897</v>
+        <v>29250</v>
       </c>
       <c r="H6" t="n">
-        <v>20059</v>
+        <v>10047</v>
       </c>
       <c r="I6" t="n">
-        <v>517</v>
+        <v>360</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12924</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10697</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21742</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13954</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>966</v>
+        <v>949</v>
       </c>
       <c r="F7" t="n">
-        <v>41180</v>
+        <v>35719</v>
       </c>
       <c r="G7" t="n">
-        <v>74168</v>
+        <v>40517</v>
       </c>
       <c r="H7" t="n">
-        <v>883331</v>
+        <v>419194</v>
       </c>
       <c r="I7" t="n">
-        <v>18458</v>
+        <v>12768</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1624</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59290</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15136</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>257</v>
+        <v>168</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>406</v>
+        <v>356</v>
       </c>
       <c r="G8" t="n">
-        <v>871</v>
+        <v>581</v>
       </c>
       <c r="H8" t="n">
-        <v>53717</v>
+        <v>31278</v>
       </c>
       <c r="I8" t="n">
-        <v>331177</v>
+        <v>160798</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
